--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0483455-CBD9-4A43-9100-5958D6568C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BDBE8F-0A28-5C48-A1E2-06ED73004FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -161,6 +161,9 @@
   </si>
   <si>
     <t>PERSISTENT</t>
+  </si>
+  <si>
+    <t>TCS</t>
   </si>
 </sst>
 </file>
@@ -227,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -238,6 +241,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1368,14 +1373,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.83203125" style="1" customWidth="1"/>
     <col min="3" max="5" width="15.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="1"/>
+    <col min="6" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1408,7 +1412,7 @@
       <c r="D2" s="5">
         <v>110</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="10">
         <v>450.2</v>
       </c>
     </row>
@@ -1423,10 +1427,10 @@
         <v>6</v>
       </c>
       <c r="D3" s="5">
-        <v>190</v>
-      </c>
-      <c r="E3" s="5">
-        <v>519.33000000000004</v>
+        <v>286</v>
+      </c>
+      <c r="E3" s="10">
+        <v>523.46874125874126</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1440,10 +1444,10 @@
         <v>7</v>
       </c>
       <c r="D4" s="5">
-        <v>2082</v>
-      </c>
-      <c r="E4" s="5">
-        <v>47.87</v>
+        <v>3148</v>
+      </c>
+      <c r="E4" s="10">
+        <v>47.754866581956797</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1457,10 +1461,10 @@
         <v>8</v>
       </c>
       <c r="D5" s="5">
-        <v>118</v>
-      </c>
-      <c r="E5" s="5">
-        <v>836.01</v>
+        <v>178</v>
+      </c>
+      <c r="E5" s="10">
+        <v>827.13134831460673</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1476,7 +1480,7 @@
       <c r="D6" s="5">
         <v>125</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="10">
         <v>398.55</v>
       </c>
     </row>
@@ -1491,10 +1495,10 @@
         <v>10</v>
       </c>
       <c r="D7" s="5">
-        <v>63</v>
-      </c>
-      <c r="E7" s="5">
-        <v>1172.02</v>
+        <v>107</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1154.4528971962616</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1510,7 +1514,7 @@
       <c r="D8" s="5">
         <v>104</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="10">
         <v>477.57</v>
       </c>
     </row>
@@ -1525,10 +1529,10 @@
         <v>12</v>
       </c>
       <c r="D9" s="5">
-        <v>54</v>
-      </c>
-      <c r="E9" s="5">
-        <v>918.7</v>
+        <v>110</v>
+      </c>
+      <c r="E9" s="10">
+        <v>891.98290909090906</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1544,7 +1548,7 @@
       <c r="D10" s="5">
         <v>132</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="10">
         <v>378.1</v>
       </c>
     </row>
@@ -1561,7 +1565,7 @@
       <c r="D11" s="5">
         <v>108</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="10">
         <v>462</v>
       </c>
     </row>
@@ -1578,7 +1582,7 @@
       <c r="D12" s="5">
         <v>107</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="10">
         <v>464.65</v>
       </c>
     </row>
@@ -1593,10 +1597,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="5">
-        <v>3602</v>
-      </c>
-      <c r="E13" s="5">
-        <v>27.73</v>
+        <v>5502</v>
+      </c>
+      <c r="E13" s="10">
+        <v>26.928836786623052</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1612,7 +1616,7 @@
       <c r="D14" s="5">
         <v>77</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="10">
         <v>646.65</v>
       </c>
     </row>
@@ -1629,7 +1633,7 @@
       <c r="D15" s="5">
         <v>42</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="10">
         <v>1171.9000000000001</v>
       </c>
     </row>
@@ -1644,10 +1648,10 @@
         <v>19</v>
       </c>
       <c r="D16" s="5">
-        <v>248</v>
-      </c>
-      <c r="E16" s="5">
-        <v>400.47</v>
+        <v>372</v>
+      </c>
+      <c r="E16" s="10">
+        <v>395</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1661,10 +1665,10 @@
         <v>32</v>
       </c>
       <c r="D17" s="3">
-        <v>61</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1197.69</v>
+        <v>103</v>
+      </c>
+      <c r="E17" s="10">
+        <v>1176.6533009708737</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1680,7 +1684,7 @@
       <c r="D18" s="3">
         <v>59</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="10">
         <v>842.4</v>
       </c>
     </row>
@@ -1695,10 +1699,10 @@
         <v>34</v>
       </c>
       <c r="D19" s="3">
-        <v>16</v>
-      </c>
-      <c r="E19" s="3">
-        <v>4365.25</v>
+        <v>28</v>
+      </c>
+      <c r="E19" s="10">
+        <v>4274.778571428571</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1714,7 +1718,7 @@
       <c r="D20" s="3">
         <v>29</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="10">
         <v>1695.5</v>
       </c>
     </row>
@@ -1729,10 +1733,10 @@
         <v>36</v>
       </c>
       <c r="D21" s="3">
-        <v>51</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1460.08</v>
+        <v>102</v>
+      </c>
+      <c r="E21" s="10">
+        <v>1430.49</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1746,10 +1750,10 @@
         <v>40</v>
       </c>
       <c r="D22" s="9">
-        <v>1542</v>
-      </c>
-      <c r="E22" s="9">
-        <v>32.409999999999997</v>
+        <v>5546</v>
+      </c>
+      <c r="E22" s="11">
+        <v>31.543645870897944</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1763,10 +1767,27 @@
         <v>41</v>
       </c>
       <c r="D23" s="9">
-        <v>8</v>
-      </c>
-      <c r="E23" s="9">
-        <v>5098.8500000000004</v>
+        <v>18</v>
+      </c>
+      <c r="E23" s="11">
+        <v>4972.4888888888891</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="9">
+        <v>25</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="9">
+        <v>51</v>
+      </c>
+      <c r="E24" s="11">
+        <v>2296.33</v>
       </c>
     </row>
   </sheetData>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manthan Patel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BDBE8F-0A28-5C48-A1E2-06ED73004FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC8D64B-A663-4598-AF3F-CF54B15096BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -52,109 +51,19 @@
     <t>AVERAGE PRICE</t>
   </si>
   <si>
-    <t>AMBUJACEM</t>
-  </si>
-  <si>
-    <t>BALRAMCHIN</t>
-  </si>
-  <si>
-    <t>DWARKESH</t>
-  </si>
-  <si>
-    <t>EIDPARRY</t>
-  </si>
-  <si>
-    <t>INDUSTOWER</t>
-  </si>
-  <si>
     <t>INFY</t>
-  </si>
-  <si>
-    <t>JUBLFOOD</t>
   </si>
   <si>
     <t>KFINTECH</t>
   </si>
   <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>PATANJALI</t>
-  </si>
-  <si>
-    <t>PFC</t>
-  </si>
-  <si>
-    <t>RENUKA</t>
-  </si>
-  <si>
-    <t>SBICARD</t>
-  </si>
-  <si>
-    <t>TATACONSUM</t>
-  </si>
-  <si>
-    <t>TRIVENI</t>
-  </si>
-  <si>
-    <t>AMBUJA CEMENT</t>
-  </si>
-  <si>
-    <t>BALRAMPUR CHINNI</t>
-  </si>
-  <si>
-    <t>DWARKESH SUGAR</t>
-  </si>
-  <si>
-    <t>EID PARRY</t>
-  </si>
-  <si>
-    <t>INDUS TOWER</t>
-  </si>
-  <si>
-    <t>INFOSYS</t>
-  </si>
-  <si>
-    <t>JUBILANT FOOODS</t>
-  </si>
-  <si>
-    <t>KOTAK BANK</t>
-  </si>
-  <si>
-    <t>RENUKA SUGAR</t>
-  </si>
-  <si>
-    <t>SBI CARDS</t>
-  </si>
-  <si>
-    <t>TATA CONSUMER</t>
-  </si>
-  <si>
-    <t>TRIVENI ENGINEERING</t>
-  </si>
-  <si>
     <t>HCLTECH</t>
-  </si>
-  <si>
-    <t>INDIANB</t>
   </si>
   <si>
     <t>LTM</t>
   </si>
   <si>
-    <t>MFSL</t>
-  </si>
-  <si>
     <t>TECHM</t>
-  </si>
-  <si>
-    <t>HCLT TECHNOLOGIES</t>
-  </si>
-  <si>
-    <t>INDIAN BANK</t>
-  </si>
-  <si>
-    <t>TECH MAHINDRA</t>
   </si>
   <si>
     <t>ITIETF</t>
@@ -170,7 +79,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -178,17 +87,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
@@ -230,19 +128,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1373,16 +1264,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="46.83203125" style="1" customWidth="1"/>
-    <col min="3" max="5" width="15.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" style="1" customWidth="1"/>
+    <col min="3" max="5" width="15.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1399,395 +1290,140 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="5">
-        <v>110</v>
-      </c>
-      <c r="E2" s="10">
-        <v>450.2</v>
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4">
+        <v>135</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1162.24</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="5">
-        <v>286</v>
-      </c>
-      <c r="E3" s="10">
-        <v>523.46874125874126</v>
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="4">
+        <v>143</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1140.76</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="5">
-        <v>3148</v>
-      </c>
-      <c r="E4" s="10">
-        <v>47.754866581956797</v>
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4">
+        <v>6866</v>
+      </c>
+      <c r="E4" s="4">
+        <v>31.29</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="5">
-        <v>178</v>
-      </c>
-      <c r="E5" s="10">
-        <v>827.13134831460673</v>
+        <v>6</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4">
+        <v>110</v>
+      </c>
+      <c r="E5" s="4">
+        <v>891.99</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="5">
-        <v>125</v>
-      </c>
-      <c r="E6" s="10">
-        <v>398.55</v>
+        <v>8</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4">
+        <v>36</v>
+      </c>
+      <c r="E6" s="4">
+        <v>4203.54</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="5">
-        <v>107</v>
-      </c>
-      <c r="E7" s="10">
-        <v>1154.4528971962616</v>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4">
+        <v>26</v>
+      </c>
+      <c r="E7" s="4">
+        <v>4869.62</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="5">
-        <v>104</v>
-      </c>
-      <c r="E8" s="10">
-        <v>477.57</v>
+        <v>12</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="4">
+        <v>67</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2280.2600000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="5">
-        <v>110</v>
-      </c>
-      <c r="E9" s="10">
-        <v>891.98290909090906</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="5">
-        <v>132</v>
-      </c>
-      <c r="E10" s="10">
-        <v>378.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>12</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="5">
-        <v>108</v>
-      </c>
-      <c r="E11" s="10">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
-        <v>13</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="5">
-        <v>107</v>
-      </c>
-      <c r="E12" s="10">
-        <v>464.65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
-        <v>14</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="5">
-        <v>5502</v>
-      </c>
-      <c r="E13" s="10">
-        <v>26.928836786623052</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
-        <v>15</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="5">
-        <v>77</v>
-      </c>
-      <c r="E14" s="10">
-        <v>646.65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
-        <v>16</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="5">
-        <v>42</v>
-      </c>
-      <c r="E15" s="10">
-        <v>1171.9000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
-        <v>17</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="5">
-        <v>372</v>
-      </c>
-      <c r="E16" s="10">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
-        <v>18</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="3">
-        <v>103</v>
-      </c>
-      <c r="E17" s="10">
-        <v>1176.6533009708737</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
-        <v>19</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="3">
-        <v>59</v>
-      </c>
-      <c r="E18" s="10">
-        <v>842.4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
-        <v>20</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="3">
-        <v>28</v>
-      </c>
-      <c r="E19" s="10">
-        <v>4274.778571428571</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
-        <v>21</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="3">
-        <v>29</v>
-      </c>
-      <c r="E20" s="10">
-        <v>1695.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
-        <v>22</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="3">
-        <v>102</v>
-      </c>
-      <c r="E21" s="10">
-        <v>1430.49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
-        <v>23</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="9">
-        <v>5546</v>
-      </c>
-      <c r="E22" s="11">
-        <v>31.543645870897944</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
-        <v>24</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="9">
-        <v>18</v>
-      </c>
-      <c r="E23" s="11">
-        <v>4972.4888888888891</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="9">
-        <v>25</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="9">
-        <v>51</v>
-      </c>
-      <c r="E24" s="11">
-        <v>2296.33</v>
+      <c r="C9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="4">
+        <v>130</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1410.95</v>
       </c>
     </row>
   </sheetData>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manthan Patel\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC8D64B-A663-4598-AF3F-CF54B15096BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064E9578-1E85-0241-BF01-1AAC99573EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28800" yWindow="-2660" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
@@ -51,28 +51,28 @@
     <t>AVERAGE PRICE</t>
   </si>
   <si>
-    <t>INFY</t>
-  </si>
-  <si>
     <t>KFINTECH</t>
   </si>
   <si>
-    <t>HCLTECH</t>
+    <t>ALKEM</t>
   </si>
   <si>
-    <t>LTM</t>
+    <t>DMART</t>
   </si>
   <si>
-    <t>TECHM</t>
+    <t>HAVELLS</t>
   </si>
   <si>
-    <t>ITIETF</t>
+    <t>MUTHOOTFIN</t>
   </si>
   <si>
-    <t>PERSISTENT</t>
+    <t>NSDL</t>
   </si>
   <si>
-    <t>TCS</t>
+    <t>RVNL</t>
+  </si>
+  <si>
+    <t>SWIGGY</t>
   </si>
 </sst>
 </file>
@@ -1265,15 +1265,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" style="1" customWidth="1"/>
-    <col min="3" max="5" width="15.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="46.83203125" style="1" customWidth="1"/>
+    <col min="3" max="5" width="15.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1290,66 +1290,66 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="4">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="E2" s="4">
-        <v>1162.24</v>
+        <v>5359.45</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" s="4">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="E3" s="4">
-        <v>1140.76</v>
+        <v>4118.2299999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="4">
-        <v>6866</v>
+        <v>85</v>
       </c>
       <c r="E4" s="4">
-        <v>31.29</v>
+        <v>1170</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="4">
         <v>110</v>
@@ -1358,72 +1358,72 @@
         <v>891.99</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="4">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E6" s="4">
-        <v>4203.54</v>
+        <v>3265.5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="4">
-        <v>26</v>
+        <v>560</v>
       </c>
       <c r="E7" s="4">
-        <v>4869.62</v>
+        <v>805.92</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" s="4">
-        <v>67</v>
+        <v>410</v>
       </c>
       <c r="E8" s="4">
-        <v>2280.2600000000002</v>
+        <v>244.5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" s="4">
-        <v>130</v>
+        <v>1580</v>
       </c>
       <c r="E9" s="4">
-        <v>1410.95</v>
+        <v>253.09</v>
       </c>
     </row>
   </sheetData>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064E9578-1E85-0241-BF01-1AAC99573EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0CD2EC1-7370-9D4A-86EE-61CC4EF034F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="-2660" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28800" yWindow="-2160" windowWidth="38400" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -74,12 +74,15 @@
   <si>
     <t>SWIGGY</t>
   </si>
+  <si>
+    <t>NSDL.BO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -87,6 +90,12 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
@@ -128,12 +137,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1382,8 +1392,8 @@
       <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>10</v>
+      <c r="C7" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="D7" s="4">
         <v>560</v>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E8437C7-9C8D-1E46-9163-77330FA8EFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99545C96-1BEC-5C49-84AC-DB7E294067FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -166,6 +166,12 @@
   </si>
   <si>
     <t>TRUECOLORS</t>
+  </si>
+  <si>
+    <t>TRUECOLORS.BO</t>
+  </si>
+  <si>
+    <t>NSDL.BO</t>
   </si>
 </sst>
 </file>
@@ -1504,7 +1510,7 @@
         <v>38</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D7" s="7">
         <v>560</v>
@@ -2082,7 +2088,7 @@
         <v>44</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D41" s="7">
         <v>1200</v>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99545C96-1BEC-5C49-84AC-DB7E294067FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA8145D-653B-0C48-84C4-72B2D94DDE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
@@ -178,10 +178,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
-  </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -189,12 +186,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
@@ -238,30 +229,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1430,7 +1419,7 @@
       <c r="D2" s="5">
         <v>20</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <v>5359.45</v>
       </c>
     </row>
@@ -1447,7 +1436,7 @@
       <c r="D3" s="5">
         <v>24</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="7">
         <v>4118.2299999999996</v>
       </c>
     </row>
@@ -1464,7 +1453,7 @@
       <c r="D4" s="5">
         <v>85</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <v>1170</v>
       </c>
     </row>
@@ -1478,11 +1467,11 @@
       <c r="C5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="5">
-        <v>11</v>
-      </c>
-      <c r="E5" s="6">
-        <v>843.3</v>
+      <c r="D5" s="6">
+        <v>121</v>
+      </c>
+      <c r="E5" s="7">
+        <v>887.56</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1496,10 +1485,10 @@
         <v>37</v>
       </c>
       <c r="D6" s="5">
-        <v>3</v>
-      </c>
-      <c r="E6" s="6">
-        <v>3164.8</v>
+        <v>63</v>
+      </c>
+      <c r="E6" s="7">
+        <v>3260.7</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1512,10 +1501,10 @@
       <c r="C7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>560</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>805.92</v>
       </c>
     </row>
@@ -1529,11 +1518,11 @@
       <c r="C8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="5">
-        <v>63</v>
-      </c>
-      <c r="E8" s="6">
-        <v>234.6</v>
+      <c r="D8" s="6">
+        <v>473</v>
+      </c>
+      <c r="E8" s="7">
+        <v>243.18</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1546,11 +1535,11 @@
       <c r="C9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="5">
-        <v>99</v>
-      </c>
-      <c r="E9" s="6">
-        <v>250.43</v>
+      <c r="D9" s="6">
+        <v>1679</v>
+      </c>
+      <c r="E9" s="7">
+        <v>252.93</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1563,10 +1552,10 @@
       <c r="C10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>222</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>26.91</v>
       </c>
     </row>
@@ -1580,10 +1569,10 @@
       <c r="C11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>933</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>29.04</v>
       </c>
     </row>
@@ -1597,10 +1586,10 @@
       <c r="C12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>408</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>103.65</v>
       </c>
     </row>
@@ -1617,7 +1606,7 @@
       <c r="D13" s="5">
         <v>51</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>115.1</v>
       </c>
     </row>
@@ -1631,10 +1620,10 @@
       <c r="C14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>312</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>100.41</v>
       </c>
     </row>
@@ -1648,10 +1637,10 @@
       <c r="C15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>258</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <v>23.33</v>
       </c>
     </row>
@@ -1665,10 +1654,10 @@
       <c r="C16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>195</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="7">
         <v>30.56</v>
       </c>
     </row>
@@ -1682,10 +1671,10 @@
       <c r="C17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>198</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="7">
         <v>30.43</v>
       </c>
     </row>
@@ -1699,10 +1688,10 @@
       <c r="C18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>114</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="7">
         <v>51.64</v>
       </c>
     </row>
@@ -1716,10 +1705,10 @@
       <c r="C19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="6">
         <v>318</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="7">
         <v>132.49</v>
       </c>
     </row>
@@ -1733,10 +1722,10 @@
       <c r="C20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="6">
         <v>2226</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="7">
         <v>12.18</v>
       </c>
     </row>
@@ -1750,10 +1739,10 @@
       <c r="C21" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="6">
         <v>204</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="7">
         <v>29.42</v>
       </c>
     </row>
@@ -1767,10 +1756,10 @@
       <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="6">
         <v>270</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="7">
         <v>155.85</v>
       </c>
     </row>
@@ -1787,7 +1776,7 @@
       <c r="D23" s="5">
         <v>9</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="7">
         <v>513.08000000000004</v>
       </c>
     </row>
@@ -1804,7 +1793,7 @@
       <c r="D24" s="5">
         <v>63</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="7">
         <v>94.57</v>
       </c>
     </row>
@@ -1818,10 +1807,10 @@
       <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="6">
         <v>183</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="7">
         <v>32.69</v>
       </c>
     </row>
@@ -1835,10 +1824,10 @@
       <c r="C26" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="6">
         <v>288</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="7">
         <v>346.35</v>
       </c>
     </row>
@@ -1852,10 +1841,10 @@
       <c r="C27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="6">
         <v>264</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="7">
         <v>159.52000000000001</v>
       </c>
     </row>
@@ -1869,10 +1858,10 @@
       <c r="C28" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="6">
         <v>3918</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="7">
         <v>13.57</v>
       </c>
     </row>
@@ -1886,10 +1875,10 @@
       <c r="C29" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="6">
         <v>1401</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="7">
         <v>22.89</v>
       </c>
     </row>
@@ -1903,10 +1892,10 @@
       <c r="C30" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="6">
         <v>1299</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="7">
         <v>32.54</v>
       </c>
     </row>
@@ -1920,10 +1909,10 @@
       <c r="C31" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="6">
         <v>429</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="7">
         <v>98.58</v>
       </c>
     </row>
@@ -1937,10 +1926,10 @@
       <c r="C32" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="6">
         <v>261</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="7">
         <v>22.87</v>
       </c>
     </row>
@@ -1957,7 +1946,7 @@
       <c r="D33" s="5">
         <v>78</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="7">
         <v>75.97</v>
       </c>
     </row>
@@ -1971,10 +1960,10 @@
       <c r="C34" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="6">
         <v>1893</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="7">
         <v>16.920000000000002</v>
       </c>
     </row>
@@ -1991,7 +1980,7 @@
       <c r="D35" s="5">
         <v>21</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="7">
         <v>263.25</v>
       </c>
     </row>
@@ -2005,10 +1994,10 @@
       <c r="C36" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="6">
         <v>531</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="7">
         <v>11.29</v>
       </c>
     </row>
@@ -2025,7 +2014,7 @@
       <c r="D37" s="5">
         <v>72</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="7">
         <v>81.67</v>
       </c>
     </row>
@@ -2039,10 +2028,10 @@
       <c r="C38" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="6">
         <v>228</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="7">
         <v>26.23</v>
       </c>
     </row>
@@ -2056,10 +2045,10 @@
       <c r="C39" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="6">
         <v>165</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="7">
         <v>258.12</v>
       </c>
     </row>
@@ -2076,7 +2065,7 @@
       <c r="D40" s="5">
         <v>72</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="7">
         <v>81.36</v>
       </c>
     </row>
@@ -2090,10 +2079,10 @@
       <c r="C41" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="6">
         <v>1200</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="7">
         <v>140.44999999999999</v>
       </c>
     </row>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA8145D-653B-0C48-84C4-72B2D94DDE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{826BA4D0-CE5F-2742-A473-AC9FF06D6E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="46">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -160,9 +160,6 @@
   </si>
   <si>
     <t>HNGSNGBEES</t>
-  </si>
-  <si>
-    <t>KALYANKJIL</t>
   </si>
   <si>
     <t>TRUECOLORS</t>
@@ -1379,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
@@ -1499,7 +1496,7 @@
         <v>38</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="6">
         <v>560</v>
@@ -1816,273 +1813,256 @@
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="D26" s="6">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="E26" s="7">
-        <v>346.35</v>
+        <v>159.52000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" s="6">
-        <v>264</v>
+        <v>3918</v>
       </c>
       <c r="E27" s="7">
-        <v>159.52000000000001</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D28" s="6">
-        <v>3918</v>
+        <v>1401</v>
       </c>
       <c r="E28" s="7">
-        <v>13.57</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D29" s="6">
-        <v>1401</v>
+        <v>1299</v>
       </c>
       <c r="E29" s="7">
-        <v>22.89</v>
+        <v>32.54</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30" s="6">
-        <v>1299</v>
+        <v>429</v>
       </c>
       <c r="E30" s="7">
-        <v>32.54</v>
+        <v>98.58</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D31" s="6">
-        <v>429</v>
+        <v>261</v>
       </c>
       <c r="E31" s="7">
-        <v>98.58</v>
+        <v>22.87</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="6">
-        <v>261</v>
+        <v>22</v>
+      </c>
+      <c r="D32" s="5">
+        <v>78</v>
       </c>
       <c r="E32" s="7">
-        <v>22.87</v>
+        <v>75.97</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="5">
-        <v>78</v>
+        <v>23</v>
+      </c>
+      <c r="D33" s="6">
+        <v>1893</v>
       </c>
       <c r="E33" s="7">
-        <v>75.97</v>
+        <v>16.920000000000002</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D34" s="6">
-        <v>1893</v>
+        <v>24</v>
+      </c>
+      <c r="D34" s="5">
+        <v>21</v>
       </c>
       <c r="E34" s="7">
-        <v>16.920000000000002</v>
+        <v>263.25</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="5">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="D35" s="6">
+        <v>531</v>
       </c>
       <c r="E35" s="7">
-        <v>263.25</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D36" s="6">
-        <v>531</v>
+        <v>26</v>
+      </c>
+      <c r="D36" s="5">
+        <v>72</v>
       </c>
       <c r="E36" s="7">
-        <v>11.29</v>
+        <v>81.67</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D37" s="5">
-        <v>72</v>
+        <v>27</v>
+      </c>
+      <c r="D37" s="6">
+        <v>228</v>
       </c>
       <c r="E37" s="7">
-        <v>81.67</v>
+        <v>26.23</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D38" s="6">
-        <v>228</v>
+        <v>165</v>
       </c>
       <c r="E38" s="7">
-        <v>26.23</v>
+        <v>258.12</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="6">
-        <v>165</v>
+        <v>28</v>
+      </c>
+      <c r="D39" s="5">
+        <v>72</v>
       </c>
       <c r="E39" s="7">
-        <v>258.12</v>
+        <v>81.36</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="5">
-        <v>72</v>
+        <v>44</v>
+      </c>
+      <c r="D40" s="6">
+        <v>1200</v>
       </c>
       <c r="E40" s="7">
-        <v>81.36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
-        <v>42</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D41" s="6">
-        <v>1200</v>
-      </c>
-      <c r="E41" s="7">
         <v>140.44999999999999</v>
       </c>
     </row>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{826BA4D0-CE5F-2742-A473-AC9FF06D6E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B61C802-1D78-8042-9DE3-B0485DD9E263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -48,75 +48,156 @@
     <t>AVERAGE PRICE</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Auto ETF</t>
+  </si>
+  <si>
     <t>AUTOIETF</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Commodities ETF</t>
+  </si>
+  <si>
     <t>COMMOIETF</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Consumption ETF</t>
+  </si>
+  <si>
     <t>CONSUMIETF</t>
   </si>
   <si>
+    <t>CPSE ETF</t>
+  </si>
+  <si>
     <t>CPSEETF</t>
   </si>
   <si>
+    <t>Edelweiss BSE Capital Markets &amp; Insurance ETF</t>
+  </si>
+  <si>
     <t>ECAPINSURE</t>
   </si>
   <si>
+    <t>Mirae Asset Nifty EV and New Age Automotive ETF</t>
+  </si>
+  <si>
     <t>EVINDIA</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Financial Serv. Ex-Bank ETF</t>
+  </si>
+  <si>
     <t>FINIETF</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty FMCG ETF</t>
+  </si>
+  <si>
     <t>FMCGIETF</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Healthcare ETF</t>
+  </si>
+  <si>
     <t>HEALTHIETF</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Infrastructure ETF</t>
+  </si>
+  <si>
     <t>INFRAIETF</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty IT ETF</t>
+  </si>
+  <si>
     <t>ITIETF</t>
   </si>
   <si>
+    <t>Mirae Asset Nifty India Manufacturing ETF</t>
+  </si>
+  <si>
     <t>MAKEINDIA</t>
   </si>
   <si>
+    <t>Mirae Asset S&amp;P 500 Top 50 ETF</t>
+  </si>
+  <si>
+    <t>MASPTOP50</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Nifty Metal ETF</t>
+  </si>
+  <si>
     <t>METALIETF</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Midcap 150 ETF</t>
+  </si>
+  <si>
     <t>MIDCAPIETF</t>
   </si>
   <si>
+    <t>Kotak Nifty MNC ETF</t>
+  </si>
+  <si>
     <t>MNC</t>
   </si>
   <si>
+    <t>Motilal Oswal Nifty India Defence ETF</t>
+  </si>
+  <si>
     <t>MODEFENCE</t>
   </si>
   <si>
+    <t>MON100</t>
+  </si>
+  <si>
+    <t>Motilal Oswal Nifty 500 ETF</t>
+  </si>
+  <si>
     <t>MONIFTY500</t>
   </si>
   <si>
+    <t>Motilal Oswal Nifty Realty ETF</t>
+  </si>
+  <si>
     <t>MOREALTY</t>
   </si>
   <si>
+    <t>Motilal Oswal Nifty Smallcap 250</t>
+  </si>
+  <si>
     <t>MOSMALL250</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty 50 ETF</t>
+  </si>
+  <si>
     <t>NIFTYIETF</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Oil &amp; Gas ETF</t>
+  </si>
+  <si>
     <t>OILIETF</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty PSU Bank ETF</t>
+  </si>
+  <si>
     <t>PSUBNKIETF</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Private Bank ETF</t>
+  </si>
+  <si>
     <t>PVTBANIETF</t>
   </si>
   <si>
+    <t>Tata Nifty India Digital ETF</t>
+  </si>
+  <si>
     <t>TNIDETF</t>
   </si>
   <si>
@@ -126,49 +207,25 @@
     <t>CHEMICAL</t>
   </si>
   <si>
+    <t>Groww BSE Power ETF</t>
+  </si>
+  <si>
+    <t>Kotak Nifty Chemicals ETF</t>
+  </si>
+  <si>
     <t>GOLDIETF</t>
   </si>
   <si>
     <t>SILVERIETF</t>
   </si>
   <si>
-    <t>ALKEM</t>
-  </si>
-  <si>
-    <t>DMART</t>
-  </si>
-  <si>
-    <t>HAVELLS</t>
-  </si>
-  <si>
-    <t>KFINTECH</t>
-  </si>
-  <si>
-    <t>MUTHOOTFIN</t>
-  </si>
-  <si>
-    <t>NSDL</t>
-  </si>
-  <si>
-    <t>RVNL</t>
-  </si>
-  <si>
-    <t>SWIGGY</t>
-  </si>
-  <si>
-    <t>GROWWRAIL</t>
-  </si>
-  <si>
-    <t>HNGSNGBEES</t>
-  </si>
-  <si>
-    <t>TRUECOLORS</t>
-  </si>
-  <si>
-    <t>TRUECOLORS.BO</t>
-  </si>
-  <si>
-    <t>NSDL.BO</t>
+    <t>ICICI Prudential Gold ETF</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Silver ETF</t>
+  </si>
+  <si>
+    <t>Motilal Oswal NASDAQ 100 ETF</t>
   </si>
 </sst>
 </file>
@@ -189,9 +246,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="2">
@@ -234,18 +291,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1376,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
@@ -1408,16 +1457,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>20</v>
-      </c>
-      <c r="E2" s="7">
-        <v>5359.45</v>
+        <v>2895</v>
+      </c>
+      <c r="E2" s="5">
+        <v>23.7</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1425,16 +1474,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5">
-        <v>24</v>
-      </c>
-      <c r="E3" s="7">
-        <v>4118.2299999999996</v>
+        <v>724</v>
+      </c>
+      <c r="E3" s="5">
+        <v>87.53</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1442,16 +1491,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>85</v>
-      </c>
-      <c r="E4" s="7">
-        <v>1170</v>
+        <v>419</v>
+      </c>
+      <c r="E4" s="5">
+        <v>113.58</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1459,16 +1508,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="6">
-        <v>121</v>
-      </c>
-      <c r="E5" s="7">
-        <v>887.56</v>
+        <v>12</v>
+      </c>
+      <c r="D5" s="5">
+        <v>677</v>
+      </c>
+      <c r="E5" s="5">
+        <v>91.77</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1476,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>63</v>
-      </c>
-      <c r="E6" s="7">
-        <v>3260.7</v>
+        <v>1502</v>
+      </c>
+      <c r="E6" s="5">
+        <v>22.39</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1493,16 +1542,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="6">
-        <v>560</v>
-      </c>
-      <c r="E7" s="7">
-        <v>805.92</v>
+        <v>16</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1846</v>
+      </c>
+      <c r="E7" s="5">
+        <v>28.26</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1510,16 +1559,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="6">
-        <v>473</v>
-      </c>
-      <c r="E8" s="7">
-        <v>243.18</v>
+        <v>18</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2239</v>
+      </c>
+      <c r="E8" s="5">
+        <v>27.67</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1527,16 +1576,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="6">
-        <v>1679</v>
-      </c>
-      <c r="E9" s="7">
-        <v>252.93</v>
+        <v>20</v>
+      </c>
+      <c r="D9" s="5">
+        <v>570</v>
+      </c>
+      <c r="E9" s="5">
+        <v>56.3</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1544,526 +1593,373 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="6">
-        <v>222</v>
-      </c>
-      <c r="E10" s="7">
-        <v>26.91</v>
+        <v>22</v>
+      </c>
+      <c r="D10" s="5">
+        <v>268</v>
+      </c>
+      <c r="E10" s="5">
+        <v>146.16999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="6">
-        <v>933</v>
-      </c>
-      <c r="E11" s="7">
-        <v>29.04</v>
+        <v>24</v>
+      </c>
+      <c r="D11" s="5">
+        <v>620</v>
+      </c>
+      <c r="E11" s="5">
+        <v>87.53</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="6">
-        <v>408</v>
-      </c>
-      <c r="E12" s="7">
-        <v>103.65</v>
+        <v>26</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1742</v>
+      </c>
+      <c r="E12" s="5">
+        <v>36.6</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>51</v>
-      </c>
-      <c r="E13" s="7">
-        <v>115.1</v>
+        <v>375</v>
+      </c>
+      <c r="E13" s="5">
+        <v>140.31</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="6">
-        <v>312</v>
-      </c>
-      <c r="E14" s="7">
-        <v>100.41</v>
+        <v>30</v>
+      </c>
+      <c r="D14" s="5">
+        <v>516</v>
+      </c>
+      <c r="E14" s="5">
+        <v>55.06</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="6">
-        <v>258</v>
-      </c>
-      <c r="E15" s="7">
-        <v>23.33</v>
+        <v>32</v>
+      </c>
+      <c r="D15" s="5">
+        <v>4280</v>
+      </c>
+      <c r="E15" s="5">
+        <v>10.87</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="6">
-        <v>195</v>
-      </c>
-      <c r="E16" s="7">
-        <v>30.56</v>
+        <v>34</v>
+      </c>
+      <c r="D16" s="5">
+        <v>2868</v>
+      </c>
+      <c r="E16" s="5">
+        <v>20.75</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="6">
-        <v>198</v>
-      </c>
-      <c r="E17" s="7">
-        <v>30.43</v>
+        <v>36</v>
+      </c>
+      <c r="D17" s="5">
+        <v>2627</v>
+      </c>
+      <c r="E17" s="5">
+        <v>28.51</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="6">
-        <v>114</v>
-      </c>
-      <c r="E18" s="7">
-        <v>51.64</v>
+        <v>38</v>
+      </c>
+      <c r="D18" s="5">
+        <v>680</v>
+      </c>
+      <c r="E18" s="5">
+        <v>82.66</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="6">
-        <v>318</v>
-      </c>
-      <c r="E19" s="7">
-        <v>132.49</v>
+        <v>39</v>
+      </c>
+      <c r="D19" s="5">
+        <v>268</v>
+      </c>
+      <c r="E19" s="5">
+        <v>184.52</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="6">
-        <v>2226</v>
-      </c>
-      <c r="E20" s="7">
-        <v>12.18</v>
+        <v>41</v>
+      </c>
+      <c r="D20" s="5">
+        <v>2134</v>
+      </c>
+      <c r="E20" s="5">
+        <v>22.31</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="6">
-        <v>204</v>
-      </c>
-      <c r="E21" s="7">
-        <v>29.42</v>
+        <v>43</v>
+      </c>
+      <c r="D21" s="5">
+        <v>465</v>
+      </c>
+      <c r="E21" s="5">
+        <v>84.58</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="6">
-        <v>270</v>
-      </c>
-      <c r="E22" s="7">
-        <v>155.85</v>
+        <v>45</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2474</v>
+      </c>
+      <c r="E22" s="5">
+        <v>15.97</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D23" s="5">
-        <v>9</v>
-      </c>
-      <c r="E23" s="7">
-        <v>513.08000000000004</v>
+        <v>161</v>
+      </c>
+      <c r="E23" s="5">
+        <v>264.74</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="D24" s="5">
-        <v>63</v>
-      </c>
-      <c r="E24" s="7">
-        <v>94.57</v>
+        <v>4217</v>
+      </c>
+      <c r="E24" s="5">
+        <v>11.04</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="6">
-        <v>183</v>
-      </c>
-      <c r="E25" s="7">
-        <v>32.69</v>
+        <v>51</v>
+      </c>
+      <c r="D25" s="5">
+        <v>983</v>
+      </c>
+      <c r="E25" s="5">
+        <v>70.44</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="6">
-        <v>264</v>
-      </c>
-      <c r="E26" s="7">
-        <v>159.52000000000001</v>
+        <v>53</v>
+      </c>
+      <c r="D26" s="5">
+        <v>2507</v>
+      </c>
+      <c r="E26" s="5">
+        <v>26.06</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="6">
-        <v>3918</v>
-      </c>
-      <c r="E27" s="7">
-        <v>13.57</v>
+        <v>55</v>
+      </c>
+      <c r="D27" s="5">
+        <v>608</v>
+      </c>
+      <c r="E27" s="5">
+        <v>85.75</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="6">
-        <v>1401</v>
-      </c>
-      <c r="E28" s="7">
-        <v>22.89</v>
+        <v>56</v>
+      </c>
+      <c r="D28" s="5">
+        <v>918</v>
+      </c>
+      <c r="E28" s="5">
+        <v>11.05</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="6">
-        <v>1299</v>
-      </c>
-      <c r="E29" s="7">
-        <v>32.54</v>
+        <v>57</v>
+      </c>
+      <c r="D29" s="5">
+        <v>355</v>
+      </c>
+      <c r="E29" s="5">
+        <v>28.41</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
-        <v>32</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="6">
-        <v>429</v>
-      </c>
-      <c r="E30" s="7">
-        <v>98.58</v>
+        <v>29</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="5">
+        <v>291</v>
+      </c>
+      <c r="E30" s="5">
+        <v>111.35</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
-        <v>33</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="6">
-        <v>261</v>
-      </c>
-      <c r="E31" s="7">
-        <v>22.87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
-        <v>34</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" s="5">
-        <v>78</v>
-      </c>
-      <c r="E32" s="7">
-        <v>75.97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
-        <v>35</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D33" s="6">
-        <v>1893</v>
-      </c>
-      <c r="E33" s="7">
-        <v>16.920000000000002</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
-        <v>36</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="5">
-        <v>21</v>
-      </c>
-      <c r="E34" s="7">
-        <v>263.25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
-        <v>37</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D35" s="6">
-        <v>531</v>
-      </c>
-      <c r="E35" s="7">
-        <v>11.29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="3">
-        <v>38</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D36" s="5">
-        <v>72</v>
-      </c>
-      <c r="E36" s="7">
-        <v>81.67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="3">
-        <v>39</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" s="6">
-        <v>228</v>
-      </c>
-      <c r="E37" s="7">
-        <v>26.23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
-        <v>40</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="6">
-        <v>165</v>
-      </c>
-      <c r="E38" s="7">
-        <v>258.12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
-        <v>41</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" s="5">
-        <v>72</v>
-      </c>
-      <c r="E39" s="7">
-        <v>81.36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
-        <v>42</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" s="6">
-        <v>1200</v>
-      </c>
-      <c r="E40" s="7">
-        <v>140.44999999999999</v>
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="5">
+        <v>159</v>
+      </c>
+      <c r="E31" s="5">
+        <v>155.79</v>
       </c>
     </row>
   </sheetData>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B61C802-1D78-8042-9DE3-B0485DD9E263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F13C92B5-637E-194D-8F20-A9E5D9865A9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -120,12 +120,6 @@
     <t>MAKEINDIA</t>
   </si>
   <si>
-    <t>Mirae Asset S&amp;P 500 Top 50 ETF</t>
-  </si>
-  <si>
-    <t>MASPTOP50</t>
-  </si>
-  <si>
     <t>ICICI Prudential Nifty Metal ETF</t>
   </si>
   <si>
@@ -150,9 +144,6 @@
     <t>MODEFENCE</t>
   </si>
   <si>
-    <t>MON100</t>
-  </si>
-  <si>
     <t>Motilal Oswal Nifty 500 ETF</t>
   </si>
   <si>
@@ -223,9 +214,6 @@
   </si>
   <si>
     <t>ICICI Prudential Silver ETF</t>
-  </si>
-  <si>
-    <t>Motilal Oswal NASDAQ 100 ETF</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
@@ -1658,7 +1646,7 @@
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>29</v>
@@ -1667,15 +1655,15 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>516</v>
+        <v>4280</v>
       </c>
       <c r="E14" s="5">
-        <v>55.06</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>31</v>
@@ -1684,15 +1672,15 @@
         <v>32</v>
       </c>
       <c r="D15" s="5">
-        <v>4280</v>
+        <v>2868</v>
       </c>
       <c r="E15" s="5">
-        <v>10.87</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>33</v>
@@ -1701,15 +1689,15 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>2868</v>
+        <v>2627</v>
       </c>
       <c r="E16" s="5">
-        <v>20.75</v>
+        <v>28.51</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>35</v>
@@ -1718,15 +1706,15 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>2627</v>
+        <v>680</v>
       </c>
       <c r="E17" s="5">
-        <v>28.51</v>
+        <v>82.66</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>37</v>
@@ -1735,230 +1723,196 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>680</v>
+        <v>2134</v>
       </c>
       <c r="E18" s="5">
-        <v>82.66</v>
+        <v>22.31</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>268</v>
+        <v>465</v>
       </c>
       <c r="E19" s="5">
-        <v>184.52</v>
+        <v>84.58</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D20" s="5">
-        <v>2134</v>
+        <v>2474</v>
       </c>
       <c r="E20" s="5">
-        <v>22.31</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D21" s="5">
-        <v>465</v>
+        <v>161</v>
       </c>
       <c r="E21" s="5">
-        <v>84.58</v>
+        <v>264.74</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D22" s="5">
-        <v>2474</v>
+        <v>4217</v>
       </c>
       <c r="E22" s="5">
-        <v>15.97</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D23" s="5">
-        <v>161</v>
+        <v>983</v>
       </c>
       <c r="E23" s="5">
-        <v>264.74</v>
+        <v>70.44</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D24" s="5">
-        <v>4217</v>
+        <v>2507</v>
       </c>
       <c r="E24" s="5">
-        <v>11.04</v>
+        <v>26.06</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D25" s="5">
-        <v>983</v>
+        <v>608</v>
       </c>
       <c r="E25" s="5">
-        <v>70.44</v>
+        <v>85.75</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>53</v>
       </c>
       <c r="D26" s="5">
-        <v>2507</v>
+        <v>918</v>
       </c>
       <c r="E26" s="5">
-        <v>26.06</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="D27" s="5">
-        <v>608</v>
+        <v>355</v>
       </c>
       <c r="E27" s="5">
-        <v>85.75</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>56</v>
+        <v>29</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="D28" s="5">
-        <v>918</v>
+        <v>291</v>
       </c>
       <c r="E28" s="5">
-        <v>11.05</v>
+        <v>111.35</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>28</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>57</v>
+        <v>30</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="D29" s="5">
-        <v>355</v>
+        <v>159</v>
       </c>
       <c r="E29" s="5">
-        <v>28.41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
-        <v>29</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="5">
-        <v>291</v>
-      </c>
-      <c r="E30" s="5">
-        <v>111.35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
-        <v>30</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="5">
-        <v>159</v>
-      </c>
-      <c r="E31" s="5">
         <v>155.79</v>
       </c>
     </row>
